--- a/src/main/kotlin/com/kcvn/spm/assets/template/ImportInventoryProduct.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ImportInventoryProduct.xlsx
@@ -24,9 +24,6 @@
     <t>Số lớp</t>
   </si>
   <si>
-    <t>Ngày tồn kho</t>
-  </si>
-  <si>
     <t>Mã công đoạn</t>
   </si>
   <si>
@@ -36,16 +33,19 @@
     <t>Số lô tấm nguyên liệu</t>
   </si>
   <si>
-    <t>Tên sản phẩn KC</t>
-  </si>
-  <si>
     <t>Số đơn đặt hàng chế tạo</t>
   </si>
   <si>
-    <t>Số tấm thành phần</t>
-  </si>
-  <si>
-    <t>Sô tấm nguyên liệu</t>
+    <t>Tên sản phẩm KC</t>
+  </si>
+  <si>
+    <t>Số tấm thành phẩm</t>
+  </si>
+  <si>
+    <t>Số tấm nguyên liệu</t>
+  </si>
+  <si>
+    <t>Tên công đoạn</t>
   </si>
 </sst>
 </file>
@@ -427,28 +427,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
